--- a/New_Ds/production_scheduling/planning_methode2_operateurs_calcules.xlsx
+++ b/New_Ds/production_scheduling/planning_methode2_operateurs_calcules.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F96"/>
+  <dimension ref="A1:H96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Priorité EDD</t>
+          <t>Date échéance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Poids</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Score</t>
         </is>
       </c>
     </row>
@@ -482,8 +492,16 @@
       <c r="E2" t="n">
         <v>2</v>
       </c>
-      <c r="F2" t="n">
-        <v>1</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="3">
@@ -506,8 +524,16 @@
       <c r="E3" t="n">
         <v>2</v>
       </c>
-      <c r="F3" t="n">
-        <v>1</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="4">
@@ -530,8 +556,16 @@
       <c r="E4" t="n">
         <v>2</v>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="5">
@@ -554,8 +588,16 @@
       <c r="E5" t="n">
         <v>1</v>
       </c>
-      <c r="F5" t="n">
-        <v>1</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="6">
@@ -578,8 +620,16 @@
       <c r="E6" t="n">
         <v>2</v>
       </c>
-      <c r="F6" t="n">
-        <v>1</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="7">
@@ -602,8 +652,16 @@
       <c r="E7" t="n">
         <v>2</v>
       </c>
-      <c r="F7" t="n">
-        <v>1</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="8">
@@ -626,8 +684,16 @@
       <c r="E8" t="n">
         <v>2</v>
       </c>
-      <c r="F8" t="n">
-        <v>1</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="9">
@@ -650,8 +716,16 @@
       <c r="E9" t="n">
         <v>1</v>
       </c>
-      <c r="F9" t="n">
-        <v>1</v>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="10">
@@ -674,8 +748,16 @@
       <c r="E10" t="n">
         <v>2</v>
       </c>
-      <c r="F10" t="n">
-        <v>1</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="11">
@@ -698,8 +780,16 @@
       <c r="E11" t="n">
         <v>2</v>
       </c>
-      <c r="F11" t="n">
-        <v>1</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="12">
@@ -722,8 +812,16 @@
       <c r="E12" t="n">
         <v>2</v>
       </c>
-      <c r="F12" t="n">
-        <v>1</v>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="13">
@@ -746,8 +844,16 @@
       <c r="E13" t="n">
         <v>1</v>
       </c>
-      <c r="F13" t="n">
-        <v>1</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="14">
@@ -770,8 +876,16 @@
       <c r="E14" t="n">
         <v>2</v>
       </c>
-      <c r="F14" t="n">
-        <v>1</v>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="15">
@@ -794,8 +908,16 @@
       <c r="E15" t="n">
         <v>2</v>
       </c>
-      <c r="F15" t="n">
-        <v>1</v>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="16">
@@ -818,8 +940,16 @@
       <c r="E16" t="n">
         <v>2</v>
       </c>
-      <c r="F16" t="n">
-        <v>1</v>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="17">
@@ -836,14 +966,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>M400229</t>
+          <t>M400200</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.174</v>
       </c>
     </row>
     <row r="18">
@@ -860,14 +998,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>M400229</t>
+          <t>M400200</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.174</v>
       </c>
     </row>
     <row r="19">
@@ -884,14 +1030,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>M400229</t>
+          <t>M400200</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.174</v>
       </c>
     </row>
     <row r="20">
@@ -908,14 +1062,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>M400229</t>
+          <t>M400200</t>
         </is>
       </c>
       <c r="E20" t="n">
         <v>1</v>
       </c>
-      <c r="F20" t="n">
-        <v>1</v>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.174</v>
       </c>
     </row>
     <row r="21">
@@ -927,19 +1089,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>OP2</t>
+          <t>OP1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>M400229</t>
+          <t>M400200</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.174</v>
       </c>
     </row>
     <row r="22">
@@ -951,19 +1121,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>OP2</t>
+          <t>OP1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>M400229</t>
+          <t>M400200</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.174</v>
       </c>
     </row>
     <row r="23">
@@ -975,19 +1153,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>OP2</t>
+          <t>OP1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>M400229</t>
+          <t>M400200</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.174</v>
       </c>
     </row>
     <row r="24">
@@ -999,19 +1185,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>OP2</t>
+          <t>OP1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>M400229</t>
+          <t>M400200</t>
         </is>
       </c>
       <c r="E24" t="n">
         <v>1</v>
       </c>
-      <c r="F24" t="n">
-        <v>1</v>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.174</v>
       </c>
     </row>
     <row r="25">
@@ -1023,19 +1217,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>OP8</t>
+          <t>OP1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>M400229</t>
+          <t>M400200</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.174</v>
       </c>
     </row>
     <row r="26">
@@ -1047,19 +1249,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>OP8</t>
+          <t>OP1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>M400229</t>
+          <t>M400200</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.174</v>
       </c>
     </row>
     <row r="27">
@@ -1071,19 +1281,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>OP8</t>
+          <t>OP1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>M400229</t>
+          <t>M400201</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>4</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.185</v>
       </c>
     </row>
     <row r="28">
@@ -1095,19 +1313,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>OP8</t>
+          <t>OP1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>M400229</t>
+          <t>M400201</t>
         </is>
       </c>
       <c r="E28" t="n">
         <v>1</v>
       </c>
-      <c r="F28" t="n">
-        <v>1</v>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>4</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.185</v>
       </c>
     </row>
     <row r="29">
@@ -1119,19 +1345,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>OP10</t>
+          <t>OP1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>M400229</t>
+          <t>M400201</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>4</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.185</v>
       </c>
     </row>
     <row r="30">
@@ -1143,19 +1377,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>OP10</t>
+          <t>OP1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>M400229</t>
+          <t>M400201</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>4</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.185</v>
       </c>
     </row>
     <row r="31">
@@ -1167,19 +1409,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>OP10</t>
+          <t>OP1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>M400229</t>
+          <t>M400201</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
-      </c>
-      <c r="F31" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>4</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.185</v>
       </c>
     </row>
     <row r="32">
@@ -1202,8 +1452,16 @@
       <c r="E32" t="n">
         <v>1</v>
       </c>
-      <c r="F32" t="n">
-        <v>1</v>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>4</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.185</v>
       </c>
     </row>
     <row r="33">
@@ -1226,8 +1484,16 @@
       <c r="E33" t="n">
         <v>1</v>
       </c>
-      <c r="F33" t="n">
-        <v>1</v>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>4</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.185</v>
       </c>
     </row>
     <row r="34">
@@ -1239,7 +1505,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>OP1</t>
+          <t>OP2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1250,8 +1516,16 @@
       <c r="E34" t="n">
         <v>1</v>
       </c>
-      <c r="F34" t="n">
-        <v>1</v>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>4</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.185</v>
       </c>
     </row>
     <row r="35">
@@ -1263,7 +1537,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>OP1</t>
+          <t>OP2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1274,8 +1548,16 @@
       <c r="E35" t="n">
         <v>1</v>
       </c>
-      <c r="F35" t="n">
-        <v>1</v>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>4</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.185</v>
       </c>
     </row>
     <row r="36">
@@ -1287,7 +1569,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>OP1</t>
+          <t>OP2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1298,8 +1580,16 @@
       <c r="E36" t="n">
         <v>1</v>
       </c>
-      <c r="F36" t="n">
-        <v>1</v>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>4</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.185</v>
       </c>
     </row>
     <row r="37">
@@ -1311,7 +1601,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>OP1</t>
+          <t>OP2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1322,8 +1612,16 @@
       <c r="E37" t="n">
         <v>1</v>
       </c>
-      <c r="F37" t="n">
-        <v>1</v>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>4</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.185</v>
       </c>
     </row>
     <row r="38">
@@ -1335,7 +1633,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>OP1</t>
+          <t>OP2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1346,8 +1644,16 @@
       <c r="E38" t="n">
         <v>1</v>
       </c>
-      <c r="F38" t="n">
-        <v>1</v>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>4</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.185</v>
       </c>
     </row>
     <row r="39">
@@ -1370,8 +1676,16 @@
       <c r="E39" t="n">
         <v>1</v>
       </c>
-      <c r="F39" t="n">
-        <v>1</v>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>4</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.185</v>
       </c>
     </row>
     <row r="40">
@@ -1383,19 +1697,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>OP2</t>
+          <t>OP1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>M400201</t>
+          <t>M400229</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.225</v>
       </c>
     </row>
     <row r="41">
@@ -1407,19 +1729,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>OP2</t>
+          <t>OP1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>M400201</t>
+          <t>M400229</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.225</v>
       </c>
     </row>
     <row r="42">
@@ -1431,19 +1761,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>OP2</t>
+          <t>OP1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>M400201</t>
+          <t>M400229</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>2</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.225</v>
       </c>
     </row>
     <row r="43">
@@ -1455,19 +1793,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>OP2</t>
+          <t>OP1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>M400201</t>
+          <t>M400229</t>
         </is>
       </c>
       <c r="E43" t="n">
         <v>1</v>
       </c>
-      <c r="F43" t="n">
-        <v>1</v>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>2</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.225</v>
       </c>
     </row>
     <row r="44">
@@ -1484,14 +1830,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>M400201</t>
+          <t>M400229</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.225</v>
       </c>
     </row>
     <row r="45">
@@ -1503,19 +1857,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>OP1</t>
+          <t>OP2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>M400200</t>
+          <t>M400229</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.225</v>
       </c>
     </row>
     <row r="46">
@@ -1527,19 +1889,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>OP1</t>
+          <t>OP2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>M400200</t>
+          <t>M400229</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.225</v>
       </c>
     </row>
     <row r="47">
@@ -1551,19 +1921,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>OP1</t>
+          <t>OP2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>M400200</t>
+          <t>M400229</t>
         </is>
       </c>
       <c r="E47" t="n">
         <v>1</v>
       </c>
-      <c r="F47" t="n">
-        <v>1</v>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>2</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.225</v>
       </c>
     </row>
     <row r="48">
@@ -1575,19 +1953,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>OP1</t>
+          <t>OP8</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>M400200</t>
+          <t>M400229</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.225</v>
       </c>
     </row>
     <row r="49">
@@ -1599,19 +1985,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>OP1</t>
+          <t>OP8</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>M400200</t>
+          <t>M400229</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.225</v>
       </c>
     </row>
     <row r="50">
@@ -1623,19 +2017,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>OP1</t>
+          <t>OP8</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>M400200</t>
+          <t>M400229</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
-      </c>
-      <c r="F50" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>2</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.225</v>
       </c>
     </row>
     <row r="51">
@@ -1647,19 +2049,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>OP1</t>
+          <t>OP8</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>M400200</t>
+          <t>M400229</t>
         </is>
       </c>
       <c r="E51" t="n">
         <v>1</v>
       </c>
-      <c r="F51" t="n">
-        <v>1</v>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>2</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.225</v>
       </c>
     </row>
     <row r="52">
@@ -1671,19 +2081,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>OP1</t>
+          <t>OP10</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>M400200</t>
+          <t>M400229</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>2</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.225</v>
       </c>
     </row>
     <row r="53">
@@ -1695,19 +2113,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>OP1</t>
+          <t>OP10</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>M400200</t>
+          <t>M400229</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>2</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.225</v>
       </c>
     </row>
     <row r="54">
@@ -1719,19 +2145,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>OP1</t>
+          <t>OP10</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>M400200</t>
+          <t>M400229</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
-      </c>
-      <c r="F54" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>2</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.225</v>
       </c>
     </row>
     <row r="55">
@@ -1743,19 +2177,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>OP2</t>
+          <t>OP3</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>M500325</t>
+          <t>M500304</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3</v>
-      </c>
-      <c r="F55" t="n">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>5</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.263</v>
       </c>
     </row>
     <row r="56">
@@ -1767,19 +2209,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>OP2</t>
+          <t>OP3</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>M500325</t>
+          <t>M500304</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3</v>
-      </c>
-      <c r="F56" t="n">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>5</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.263</v>
       </c>
     </row>
     <row r="57">
@@ -1791,19 +2241,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>OP2</t>
+          <t>OP3</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>M500325</t>
+          <t>M500304</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3</v>
-      </c>
-      <c r="F57" t="n">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>5</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.263</v>
       </c>
     </row>
     <row r="58">
@@ -1815,19 +2273,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>OP2</t>
+          <t>OP3</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>M500325</t>
+          <t>M500304</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3</v>
-      </c>
-      <c r="F58" t="n">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>5</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.263</v>
       </c>
     </row>
     <row r="59">
@@ -1839,7 +2305,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>OP3</t>
+          <t>OP2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1850,8 +2316,16 @@
       <c r="E59" t="n">
         <v>3</v>
       </c>
-      <c r="F59" t="n">
-        <v>2</v>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>4</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.328</v>
       </c>
     </row>
     <row r="60">
@@ -1863,7 +2337,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>OP3</t>
+          <t>OP2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1874,8 +2348,16 @@
       <c r="E60" t="n">
         <v>3</v>
       </c>
-      <c r="F60" t="n">
-        <v>2</v>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>4</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.328</v>
       </c>
     </row>
     <row r="61">
@@ -1887,7 +2369,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>OP3</t>
+          <t>OP2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1898,8 +2380,16 @@
       <c r="E61" t="n">
         <v>3</v>
       </c>
-      <c r="F61" t="n">
-        <v>2</v>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>4</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.328</v>
       </c>
     </row>
     <row r="62">
@@ -1911,7 +2401,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OP3</t>
+          <t>OP2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1920,10 +2410,18 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2</v>
-      </c>
-      <c r="F62" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>4</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.328</v>
       </c>
     </row>
     <row r="63">
@@ -1940,14 +2438,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>M500304</t>
+          <t>M500325</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5</v>
-      </c>
-      <c r="F63" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>4</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.328</v>
       </c>
     </row>
     <row r="64">
@@ -1964,14 +2470,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>M500304</t>
+          <t>M500325</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5</v>
-      </c>
-      <c r="F64" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>4</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.328</v>
       </c>
     </row>
     <row r="65">
@@ -1988,14 +2502,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>M500304</t>
+          <t>M500325</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5</v>
-      </c>
-      <c r="F65" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>4</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.328</v>
       </c>
     </row>
     <row r="66">
@@ -2012,14 +2534,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>M500304</t>
+          <t>M500325</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5</v>
-      </c>
-      <c r="F66" t="n">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>4</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.328</v>
       </c>
     </row>
     <row r="67">
@@ -2031,19 +2561,27 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>OP2</t>
+          <t>OP6</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>M500309</t>
+          <t>M502026</t>
         </is>
       </c>
       <c r="E67" t="n">
         <v>1</v>
       </c>
-      <c r="F67" t="n">
-        <v>2</v>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>5</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.45</v>
       </c>
     </row>
     <row r="68">
@@ -2066,8 +2604,16 @@
       <c r="E68" t="n">
         <v>8</v>
       </c>
-      <c r="F68" t="n">
-        <v>3</v>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>3</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.513</v>
       </c>
     </row>
     <row r="69">
@@ -2090,8 +2636,16 @@
       <c r="E69" t="n">
         <v>8</v>
       </c>
-      <c r="F69" t="n">
-        <v>3</v>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>3</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.513</v>
       </c>
     </row>
     <row r="70">
@@ -2114,8 +2668,16 @@
       <c r="E70" t="n">
         <v>8</v>
       </c>
-      <c r="F70" t="n">
-        <v>3</v>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>3</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.513</v>
       </c>
     </row>
     <row r="71">
@@ -2138,8 +2700,16 @@
       <c r="E71" t="n">
         <v>8</v>
       </c>
-      <c r="F71" t="n">
-        <v>3</v>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>3</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.513</v>
       </c>
     </row>
     <row r="72">
@@ -2151,19 +2721,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>OP3</t>
+          <t>OP5</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>M500319</t>
+          <t>M500327</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>8</v>
-      </c>
-      <c r="F72" t="n">
-        <v>3</v>
+        <v>3</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>5</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.575</v>
       </c>
     </row>
     <row r="73">
@@ -2175,19 +2753,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>OP3</t>
+          <t>OP5</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>M500319</t>
+          <t>M500327</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
-      </c>
-      <c r="F73" t="n">
-        <v>3</v>
+        <v>3</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>5</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.575</v>
       </c>
     </row>
     <row r="74">
@@ -2199,19 +2785,27 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>OP3</t>
+          <t>OP5</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>M500319</t>
+          <t>M500327</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>7</v>
-      </c>
-      <c r="F74" t="n">
-        <v>3</v>
+        <v>3</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>5</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.575</v>
       </c>
     </row>
     <row r="75">
@@ -2223,19 +2817,27 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>OP6</t>
+          <t>OP9</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>M502026</t>
+          <t>M500327</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1</v>
-      </c>
-      <c r="F75" t="n">
-        <v>3</v>
+        <v>3</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>5</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.575</v>
       </c>
     </row>
     <row r="76">
@@ -2247,19 +2849,27 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>OP4</t>
+          <t>OP9</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>M500317</t>
+          <t>M500327</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4</v>
-      </c>
-      <c r="F76" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>5</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.575</v>
       </c>
     </row>
     <row r="77">
@@ -2271,19 +2881,27 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>OP4</t>
+          <t>OP9</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>M500317</t>
+          <t>M500327</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4</v>
-      </c>
-      <c r="F77" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>5</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.575</v>
       </c>
     </row>
     <row r="78">
@@ -2295,19 +2913,27 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>OP4</t>
+          <t>OP3</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>M500317</t>
+          <t>M500319</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4</v>
-      </c>
-      <c r="F78" t="n">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>2</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.613</v>
       </c>
     </row>
     <row r="79">
@@ -2319,19 +2945,27 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>OP4</t>
+          <t>OP3</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>M500317</t>
+          <t>M500319</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1</v>
-      </c>
-      <c r="F79" t="n">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>2</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.613</v>
       </c>
     </row>
     <row r="80">
@@ -2343,19 +2977,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>OP10</t>
+          <t>OP3</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>M500317</t>
+          <t>M500319</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4</v>
-      </c>
-      <c r="F80" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>2</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.613</v>
       </c>
     </row>
     <row r="81">
@@ -2367,19 +3009,27 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>OP10</t>
+          <t>OP2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>M500317</t>
+          <t>M500309</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4</v>
-      </c>
-      <c r="F81" t="n">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.624</v>
       </c>
     </row>
     <row r="82">
@@ -2391,19 +3041,27 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>OP10</t>
+          <t>OP4</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>M500317</t>
+          <t>M500329</t>
         </is>
       </c>
       <c r="E82" t="n">
         <v>4</v>
       </c>
-      <c r="F82" t="n">
-        <v>4</v>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>4</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.638</v>
       </c>
     </row>
     <row r="83">
@@ -2415,19 +3073,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>OP4</t>
+          <t>OP5</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>M500329</t>
+          <t>M500311</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4</v>
-      </c>
-      <c r="F83" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>3</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.77</v>
       </c>
     </row>
     <row r="84">
@@ -2444,14 +3110,22 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>M500327</t>
+          <t>M500311</t>
         </is>
       </c>
       <c r="E84" t="n">
         <v>3</v>
       </c>
-      <c r="F84" t="n">
-        <v>5</v>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>3</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.77</v>
       </c>
     </row>
     <row r="85">
@@ -2463,19 +3137,27 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>OP5</t>
+          <t>OP9</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>M500327</t>
+          <t>M500311</t>
         </is>
       </c>
       <c r="E85" t="n">
         <v>3</v>
       </c>
-      <c r="F85" t="n">
-        <v>5</v>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>3</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0.77</v>
       </c>
     </row>
     <row r="86">
@@ -2487,19 +3169,27 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>OP5</t>
+          <t>OP9</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>M500327</t>
+          <t>M500311</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>3</v>
-      </c>
-      <c r="F86" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>3</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0.77</v>
       </c>
     </row>
     <row r="87">
@@ -2511,19 +3201,27 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>OP9</t>
+          <t>OP4</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>M500327</t>
+          <t>M500317</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>3</v>
-      </c>
-      <c r="F87" t="n">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.797</v>
       </c>
     </row>
     <row r="88">
@@ -2535,19 +3233,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>OP9</t>
+          <t>OP4</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>M500327</t>
+          <t>M500317</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>3</v>
-      </c>
-      <c r="F88" t="n">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0.797</v>
       </c>
     </row>
     <row r="89">
@@ -2559,19 +3265,27 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>OP9</t>
+          <t>OP4</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>M500327</t>
+          <t>M500317</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2</v>
-      </c>
-      <c r="F89" t="n">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0.797</v>
       </c>
     </row>
     <row r="90">
@@ -2583,19 +3297,27 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>OP5</t>
+          <t>OP4</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>M500311</t>
+          <t>M500317</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
-      </c>
-      <c r="F90" t="n">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.797</v>
       </c>
     </row>
     <row r="91">
@@ -2607,19 +3329,27 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>OP5</t>
+          <t>OP10</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>M500311</t>
+          <t>M500317</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3</v>
-      </c>
-      <c r="F91" t="n">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0.797</v>
       </c>
     </row>
     <row r="92">
@@ -2631,19 +3361,27 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>OP9</t>
+          <t>OP10</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>M500311</t>
+          <t>M500317</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3</v>
-      </c>
-      <c r="F92" t="n">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.797</v>
       </c>
     </row>
     <row r="93">
@@ -2655,19 +3393,27 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>OP9</t>
+          <t>OP10</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>M500311</t>
+          <t>M500317</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2</v>
-      </c>
-      <c r="F93" t="n">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.797</v>
       </c>
     </row>
     <row r="94">
@@ -2690,8 +3436,16 @@
       <c r="E94" t="n">
         <v>3</v>
       </c>
-      <c r="F94" t="n">
-        <v>5</v>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>2</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.899</v>
       </c>
     </row>
     <row r="95">
@@ -2714,8 +3468,16 @@
       <c r="E95" t="n">
         <v>3</v>
       </c>
-      <c r="F95" t="n">
-        <v>5</v>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>2</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0.899</v>
       </c>
     </row>
     <row r="96">
@@ -2738,8 +3500,16 @@
       <c r="E96" t="n">
         <v>3</v>
       </c>
-      <c r="F96" t="n">
-        <v>5</v>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>2</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0.899</v>
       </c>
     </row>
   </sheetData>
@@ -2753,7 +3523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2779,10 +3549,15 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Priorité EDD</t>
+          <t>Date échéance</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Poids</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Opérateurs capables</t>
         </is>
@@ -2803,10 +3578,15 @@
       <c r="D2" t="n">
         <v>4</v>
       </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>OP1, OP2, OP7, OP8, OP10</t>
         </is>
@@ -2815,24 +3595,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M400229</t>
+          <t>M400200</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>140.4</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>18.72</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>OP1, OP2, OP8, OP10</t>
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>OP1, OP2, OP7, OP10</t>
         </is>
       </c>
     </row>
@@ -2851,10 +3636,15 @@
       <c r="D4" t="n">
         <v>2</v>
       </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>OP1, OP2, OP10</t>
         </is>
@@ -2863,96 +3653,116 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M400200</t>
+          <t>M400229</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>140.4</v>
       </c>
       <c r="C5" t="n">
-        <v>2.666666666666667</v>
+        <v>18.72</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>OP1, OP2, OP7, OP10</t>
+        <v>4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>OP1, OP2, OP8, OP10</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M500325</t>
+          <t>M500304</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51.75</v>
+        <v>45</v>
       </c>
       <c r="C6" t="n">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>OP2, OP3, OP7, OP10</t>
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>OP3, OP7, OP10</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M500304</t>
+          <t>M500325</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>45</v>
+        <v>51.75</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>OP3, OP7, OP10</t>
+        <v>2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>OP2, OP3, OP7, OP10</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M500309</t>
+          <t>M502026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.85</v>
+        <v>2.25</v>
       </c>
       <c r="C8" t="n">
-        <v>0.38</v>
+        <v>0.3</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
-      <c r="E8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>OP2, OP3, OP7, OP10</t>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>OP6, OP10</t>
         </is>
       </c>
     </row>
@@ -2971,10 +3781,15 @@
       <c r="D9" t="n">
         <v>2</v>
       </c>
-      <c r="E9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>OP3, OP4, OP8, OP10</t>
         </is>
@@ -2983,72 +3798,87 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M500319</t>
+          <t>M500327</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>44.85</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>5.98</v>
+        <v>11.78666666666667</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>OP3, OP4, OP8, OP10</t>
+        <v>2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>OP5, OP9, OP10</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M502026</t>
+          <t>M500319</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.25</v>
+        <v>44.85</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3</v>
+        <v>5.98</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
-      <c r="E11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>OP6, OP10</t>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>OP3, OP4, OP8, OP10</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M500317</t>
+          <t>M500309</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>56.25</v>
+        <v>2.85</v>
       </c>
       <c r="C12" t="n">
-        <v>7.5</v>
+        <v>0.38</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>OP4, OP10</t>
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>OP2, OP3, OP7, OP10</t>
         </is>
       </c>
     </row>
@@ -3067,10 +3897,15 @@
       <c r="D13" t="n">
         <v>1</v>
       </c>
-      <c r="E13" t="n">
-        <v>4</v>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>OP4, OP5, OP10</t>
         </is>
@@ -3079,22 +3914,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M500327</t>
+          <t>M500311</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>88.40000000000001</v>
+        <v>57.2</v>
       </c>
       <c r="C14" t="n">
-        <v>11.78666666666667</v>
+        <v>7.626666666666667</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
-      <c r="E14" t="n">
-        <v>5</v>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>OP5, OP9, OP10</t>
         </is>
@@ -3103,24 +3943,29 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M500311</t>
+          <t>M500317</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>57.2</v>
+        <v>56.25</v>
       </c>
       <c r="C15" t="n">
-        <v>7.626666666666667</v>
+        <v>7.5</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
-      <c r="E15" t="n">
-        <v>5</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>OP5, OP9, OP10</t>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>OP4, OP10</t>
         </is>
       </c>
     </row>
@@ -3139,10 +3984,15 @@
       <c r="D16" t="n">
         <v>1</v>
       </c>
-      <c r="E16" t="n">
-        <v>5</v>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>OP5, OP9, OP10</t>
         </is>
